--- a/fixtures/corpus/hb_errors_as_values.xlsx
+++ b/fixtures/corpus/hb_errors_as_values.xlsx
@@ -43,7 +43,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="e">
@@ -119,18 +119,10 @@
     </row>
     <row r="10">
       <c r="A10" t="e">
-        <v>#GETTING_DATA</v>
-      </c>
-      <c r="B10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="e">
         <f>1/0</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="B11" t="b">
+      <c r="B10" t="b">
         <f>B1</f>
         <v>1</v>
       </c>
